--- a/fixtures/imports/templates/Items.xlsx
+++ b/fixtures/imports/templates/Items.xlsx
@@ -67,14 +67,14 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Veyra business records: Items</t>
+          <t xml:space="preserve">Veyrafy business records: Items</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Fill in one row per record on the sheet(s) of this workbook, then upload the file in Veyra under ERP → Import and export.</t>
+          <t xml:space="preserve">Fill in one row per record on the sheet(s) of this workbook, then upload the file in Veyrafy under ERP → Import and export.</t>
         </is>
       </c>
     </row>
@@ -88,14 +88,14 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Veyra checks the whole upload before anything is imported. If any row has a problem, nothing is imported: fix the rows it lists and upload again.</t>
+          <t xml:space="preserve">Veyrafy checks the whole upload before anything is imported. If any row has a problem, nothing is imported: fix the rows it lists and upload again.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">Records that already exist with the same details are skipped. Veyra never changes an existing record.</t>
+          <t xml:space="preserve">Records that already exist with the same details are skipped. Veyrafy never changes an existing record.</t>
         </is>
       </c>
     </row>
